--- a/SS3 models/APRU/06_Base_Final/bootstrap/01_tables.xlsx
+++ b/SS3 models/APRU/06_Base_Final/bootstrap/01_tables.xlsx
@@ -6,15 +6,15 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="01_Quants" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_RefPoints" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_Sensitivies" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="01_Quants" sheetId="10" state="visible" r:id="rId1"/>
+    <sheet name="02_RefPoints" sheetId="11" state="visible" r:id="rId2"/>
+    <sheet name="03_Sensitivies" sheetId="12" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
   <si>
     <t xml:space="preserve">YEAR</t>
   </si>
@@ -497,6 +497,48 @@
   </si>
   <si>
     <t xml:space="preserve">0.99 (0.99 - 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004 (0.002 - 0.009)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F2025/Fmsy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.032 (0.017 - 0.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSB2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.53 (9.22 - 34.57)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSB2025/SSBmsst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48 (3.03 - 3.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catch_2022-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32 (-0.02 - 0.65)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPR_2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96 (0.92 - 0.99)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catch_2023-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (0.08 - 0.51)</t>
   </si>
 </sst>
 </file>
@@ -2194,18 +2236,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="B4" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
@@ -2218,18 +2260,18 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8">
@@ -2242,10 +2284,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="B9" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10">
@@ -2258,10 +2300,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B11" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
